--- a/business_forms/047_manufacturing_research_liaison_contact_form--business_forms.xlsx
+++ b/business_forms/047_manufacturing_research_liaison_contact_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other (Please specify)</t>
+          <t>Manufacturing Equipment Other</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>manufacturing_process</t>
+          <t>manufacturing_process_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Manufacturing Process</t>
+          <t>Manufacturing Process 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>manufacturing_equipment</t>
+          <t>manufacturing_equipment_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Manufacturing Equipment</t>
+          <t>Manufacturing Equipment 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>manufacturing_technology</t>
+          <t>manufacturing_technology_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Manufacturing Technology</t>
+          <t>Manufacturing Technology 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>manufacturing_process_control_other</t>
+          <t>manufacturing_process_control_other_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other (Please specify)</t>
+          <t>Manufacturing Process Control Other 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>manufacturing_process_choices</t>
+          <t>manufacturing_process_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>manufacturing_process_choices</t>
+          <t>manufacturing_process_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>manufacturing_process_choices</t>
+          <t>manufacturing_process_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>manufacturing_process_choices</t>
+          <t>manufacturing_process_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>manufacturing_equipment_choices</t>
+          <t>manufacturing_equipment_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>manufacturing_equipment_choices</t>
+          <t>manufacturing_equipment_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>manufacturing_equipment_choices</t>
+          <t>manufacturing_equipment_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>manufacturing_equipment_choices</t>
+          <t>manufacturing_equipment_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
